--- a/demo/examples/studentImport/sinh_vien_test_AITA-TEST-001.xlsx
+++ b/demo/examples/studentImport/sinh_vien_test_AITA-TEST-001.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9615329F-5778-4E7D-B4BD-286136901485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sinh viên" state="visible" r:id="rId4"/>
+    <sheet name="Sinh viên" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sinh viên'!$A1:$B11</definedName>
-  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Email</t>
   </si>
@@ -56,72 +57,33 @@
   </si>
   <si>
     <t>Vũ Thị Thu Trang</t>
-  </si>
-  <si>
-    <t>student.test07@fpt.edu.vn</t>
-  </si>
-  <si>
-    <t>Đặng Quốc Bảo</t>
-  </si>
-  <si>
-    <t>student.test08@fpt.edu.vn</t>
-  </si>
-  <si>
-    <t>Bùi Khánh Linh</t>
-  </si>
-  <si>
-    <t>student.test09@fpt.edu.vn</t>
-  </si>
-  <si>
-    <t>Đỗ Hải Đăng</t>
-  </si>
-  <si>
-    <t>student.test10@fpt.edu.vn</t>
-  </si>
-  <si>
-    <t>Ngô Phương Thảo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1F2937"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D4ED8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -136,17 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,18 +439,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C942D0-63B0-482B-8147-E6B2F963D3DE}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,88 +455,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>